--- a/Docs/Sprint Retrospective.xlsx
+++ b/Docs/Sprint Retrospective.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d0d25a1f11c8555b/Desktop/SpaceLandMapper Docs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_AF2D88A55568360EEF227C564A5DCE3A77446F46" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{54C765EF-0996-4F11-BE9F-56FC15202AF8}"/>
+  <xr:revisionPtr revIDLastSave="3" documentId="11_AF2D88A55568360EEF227C564A5DCE3A77446F46" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9B82FF4E-07A5-4B2A-888B-E403D0BA8A9A}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -335,6 +335,10 @@
 </styleSheet>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
